--- a/5/search/FY4_Missile2_results/fine_tuned/top10_fine_tuned_solutions.xlsx
+++ b/5/search/FY4_Missile2_results/fine_tuned/top10_fine_tuned_solutions.xlsx
@@ -492,86 +492,86 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>292</v>
+        <v>295.4</v>
       </c>
       <c r="B2" t="n">
-        <v>122.7</v>
+        <v>105.8</v>
       </c>
       <c r="C2" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>11193.04976185096</v>
+        <v>11308.59309237556</v>
       </c>
       <c r="F2" t="n">
-        <v>1522.185072387552</v>
+        <v>1350.104456902427</v>
       </c>
       <c r="G2" t="n">
         <v>1800</v>
       </c>
       <c r="H2" t="n">
-        <v>11652.69205197228</v>
+        <v>11762.40646351609</v>
       </c>
       <c r="I2" t="n">
-        <v>384.5304828341036</v>
+        <v>394.3757170530545</v>
       </c>
       <c r="J2" t="n">
         <v>1310</v>
       </c>
       <c r="K2" t="n">
-        <v>3.599999999999998</v>
+        <v>3.699999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>301</v>
+        <v>291.2</v>
       </c>
       <c r="B3" t="n">
-        <v>102.3</v>
+        <v>124.2</v>
       </c>
       <c r="C3" t="n">
-        <v>8.6</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>11453.12019754437</v>
+        <v>11179.65508641678</v>
       </c>
       <c r="F3" t="n">
-        <v>1245.881352188296</v>
+        <v>1536.821535556134</v>
       </c>
       <c r="G3" t="n">
         <v>1800</v>
       </c>
       <c r="H3" t="n">
-        <v>11969.46646916469</v>
+        <v>11628.79280245874</v>
       </c>
       <c r="I3" t="n">
-        <v>386.5368465424002</v>
+        <v>378.8753744464673</v>
       </c>
       <c r="J3" t="n">
-        <v>1329.404</v>
+        <v>1310</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>3.600000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>294.6</v>
+        <v>293.8</v>
       </c>
       <c r="B4" t="n">
-        <v>102.3</v>
+        <v>101.8</v>
       </c>
       <c r="C4" t="n">
         <v>7.4</v>
@@ -580,25 +580,25 @@
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>11315.13288535697</v>
+        <v>11303.99874264818</v>
       </c>
       <c r="F4" t="n">
-        <v>1311.690080729188</v>
+        <v>1310.74258301537</v>
       </c>
       <c r="G4" t="n">
         <v>1800</v>
       </c>
       <c r="H4" t="n">
-        <v>11740.98813583936</v>
+        <v>11714.80785433491</v>
       </c>
       <c r="I4" t="n">
-        <v>381.5415411740378</v>
+        <v>379.3136411442485</v>
       </c>
       <c r="J4" t="n">
         <v>1310</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>3.599999999999998</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -606,75 +606,75 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>290.4</v>
+        <v>303.4</v>
       </c>
       <c r="B5" t="n">
-        <v>125.7</v>
+        <v>101.8</v>
       </c>
       <c r="C5" t="n">
-        <v>3.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>11166.49892412374</v>
+        <v>11515.558241934</v>
       </c>
       <c r="F5" t="n">
-        <v>1552.297884899303</v>
+        <v>1218.114885182024</v>
       </c>
       <c r="G5" t="n">
         <v>1800</v>
       </c>
       <c r="H5" t="n">
-        <v>11604.65398760726</v>
+        <v>12059.13595353833</v>
       </c>
       <c r="I5" t="n">
-        <v>374.1344241079953</v>
+        <v>393.7360141239405</v>
       </c>
       <c r="J5" t="n">
-        <v>1310</v>
+        <v>1338.959</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>3.599999999999998</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>292</v>
+        <v>291.2</v>
       </c>
       <c r="B6" t="n">
-        <v>125.7</v>
+        <v>119.2</v>
       </c>
       <c r="C6" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>11178.93458541105</v>
+        <v>11198.28598426741</v>
       </c>
       <c r="F6" t="n">
-        <v>1557.121360027628</v>
+        <v>1488.78821331751</v>
       </c>
       <c r="G6" t="n">
         <v>1800</v>
       </c>
       <c r="H6" t="n">
-        <v>11649.81507333485</v>
+        <v>11629.34247180527</v>
       </c>
       <c r="I6" t="n">
-        <v>391.6512548371763</v>
+        <v>377.4582422686196</v>
       </c>
       <c r="J6" t="n">
         <v>1310</v>
       </c>
       <c r="K6" t="n">
-        <v>3.400000000000002</v>
+        <v>3.599999999999998</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -682,37 +682,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>293</v>
+        <v>303.4</v>
       </c>
       <c r="B7" t="n">
-        <v>103.3</v>
+        <v>98.8</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>11282.53767901059</v>
+        <v>11532.9974717799</v>
       </c>
       <c r="F7" t="n">
-        <v>1334.38294046854</v>
+        <v>1191.666904873839</v>
       </c>
       <c r="G7" t="n">
         <v>1800</v>
       </c>
       <c r="H7" t="n">
-        <v>11686.16293474001</v>
+        <v>12060.55619384775</v>
       </c>
       <c r="I7" t="n">
-        <v>383.5014268521693</v>
+        <v>391.5821066367211</v>
       </c>
       <c r="J7" t="n">
-        <v>1310</v>
+        <v>1338.959</v>
       </c>
       <c r="K7" t="n">
-        <v>3.300000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
@@ -720,75 +720,75 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>293</v>
+        <v>292.8</v>
       </c>
       <c r="B8" t="n">
-        <v>101.3</v>
+        <v>120.2</v>
       </c>
       <c r="C8" t="n">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>11292.89986853813</v>
+        <v>11214.2651180611</v>
       </c>
       <c r="F8" t="n">
-        <v>1309.971151754982</v>
+        <v>1490.283426223686</v>
       </c>
       <c r="G8" t="n">
         <v>1800</v>
       </c>
       <c r="H8" t="n">
-        <v>11688.71050169776</v>
+        <v>11680.05885297652</v>
       </c>
       <c r="I8" t="n">
-        <v>377.4997352076595</v>
+        <v>382.2039180143088</v>
       </c>
       <c r="J8" t="n">
         <v>1310</v>
       </c>
       <c r="K8" t="n">
-        <v>3.300000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>296.2</v>
+        <v>295.4</v>
       </c>
       <c r="B9" t="n">
-        <v>103.3</v>
+        <v>95.8</v>
       </c>
       <c r="C9" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>11337.49590399107</v>
+        <v>11353.39107770818</v>
       </c>
       <c r="F9" t="n">
-        <v>1314.11775705355</v>
+        <v>1255.760118915784</v>
       </c>
       <c r="G9" t="n">
         <v>1800</v>
       </c>
       <c r="H9" t="n">
-        <v>11793.57144992494</v>
+        <v>11764.3109355084</v>
       </c>
       <c r="I9" t="n">
-        <v>387.2498611799684</v>
+        <v>390.3649083527412</v>
       </c>
       <c r="J9" t="n">
         <v>1310</v>
       </c>
       <c r="K9" t="n">
-        <v>3.300000000000001</v>
+        <v>3.400000000000002</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
@@ -796,37 +796,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>290.4</v>
+        <v>294.4</v>
       </c>
       <c r="B10" t="n">
-        <v>121.7</v>
+        <v>125.2</v>
       </c>
       <c r="C10" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>11178.16911626807</v>
+        <v>11206.88269845613</v>
       </c>
       <c r="F10" t="n">
-        <v>1520.917683891114</v>
+        <v>1543.929622668267</v>
       </c>
       <c r="G10" t="n">
         <v>1800</v>
       </c>
       <c r="H10" t="n">
-        <v>11602.38129785872</v>
+        <v>11724.08944459646</v>
       </c>
       <c r="I10" t="n">
-        <v>380.2455026794823</v>
+        <v>403.7536793389329</v>
       </c>
       <c r="J10" t="n">
         <v>1310</v>
       </c>
       <c r="K10" t="n">
-        <v>3.299999999999997</v>
+        <v>3.400000000000002</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -834,40 +834,40 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>296.2</v>
+        <v>292.8</v>
       </c>
       <c r="B11" t="n">
-        <v>98.3</v>
+        <v>125.2</v>
       </c>
       <c r="C11" t="n">
-        <v>8.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>11355.88020770131</v>
+        <v>11194.06780569521</v>
       </c>
       <c r="F11" t="n">
-        <v>1276.755918540311</v>
+        <v>1538.330933684479</v>
       </c>
       <c r="G11" t="n">
         <v>1800</v>
       </c>
       <c r="H11" t="n">
-        <v>11789.8804609956</v>
+        <v>11679.23731993325</v>
       </c>
       <c r="I11" t="n">
-        <v>394.750941150446</v>
+        <v>384.1582678956765</v>
       </c>
       <c r="J11" t="n">
         <v>1310</v>
       </c>
       <c r="K11" t="n">
-        <v>3.200000000000003</v>
+        <v>3.400000000000002</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
